--- a/data/trans_orig/IP1011-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1011-Edad-trans_orig.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4523</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>250180</t>
+          <t>250169</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>249076</t>
+          <t>249233</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>501223</t>
+          <t>500807</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>190078</t>
+          <t>190747</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>202478</t>
+          <t>202621</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>394846</t>
+          <t>395419</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>677099</t>
+          <t>675887</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>717450</t>
+          <t>717388</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1396659</t>
+          <t>1396170</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1402448</t>
+          <t>1402511</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>4809</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>230669</t>
+          <t>230966</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>263306</t>
+          <t>263310</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>497141</t>
+          <t>496767</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155502</t>
+          <t>155297</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>310101</t>
+          <t>309668</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>4475</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>168028</t>
+          <t>167005</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>345374</t>
+          <t>344819</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>701965</t>
+          <t>702115</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>743501</t>
+          <t>743100</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1448261</t>
+          <t>1448131</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1454396</t>
+          <t>1454409</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>3603</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>253997</t>
+          <t>253954</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>464314</t>
+          <t>464975</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>741281</t>
+          <t>741966</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1445116</t>
+          <t>1445301</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/IP1011-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1011-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,74 +1065,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4647</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>605</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3036</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3039</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,24%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>1,2%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4523</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>3</t>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>5452</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>252453</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>249109</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,17%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>378</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>252600</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>250169</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>250166</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,76%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>98,8%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>252453</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>249233</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,22%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>758</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>500807</t>
+          <t>501509</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1756,102 +1756,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3733</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3350</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3759</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1328</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3428</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4464</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4727</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>205382</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>202316</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>193436</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>190747</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>190338</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,06%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>205382</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>202621</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>594</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>395419</t>
+          <t>395682</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5849</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1266</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5134</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4386</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5312</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>7711</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>720730</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>716851</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>722099</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>679755</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>675887</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>676635</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>720730</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>717388</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>722098</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2099</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1396170</t>
+          <t>1396010</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1402511</t>
+          <t>1402455</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2782,47 +2782,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>146281</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3017,102 +3017,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3898</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>756</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3510</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4090</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1428</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3791</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5760</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1428</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4809</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>266429</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>263203</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,75%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,54%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>336</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>233720</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>230966</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>230386</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,68%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,26%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>266429</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>263310</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,75%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>706</t>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>496767</t>
+          <t>495816</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,107 +3355,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2653</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>651</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3274</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3244</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3737</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157920</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>155918</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>157920</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>155297</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>309668</t>
+          <t>310161</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,107 +3698,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4332</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3707</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>2661</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4475</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>170681</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>167005</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>167630</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,62%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,84%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>504</t>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>344819</t>
+          <t>346633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4046,67 +4046,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4606</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>1412</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4369</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5042</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>673</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>746819</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>743536</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,38%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>705516</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>702115</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>702559</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,8%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,38%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>746819</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>743100</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,33%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2080</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1448131</t>
+          <t>1448287</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1454409</t>
+          <t>1454397</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4729,47 +4729,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,107 +4959,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3564</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4107</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3359</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3603</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>257348</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>254497</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,62%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>257348</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>253954</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>464975</t>
+          <t>465219</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5415,47 +5415,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5758,47 +5758,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,107 +5988,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3938</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2878</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3553</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3914</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>744131</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>740906</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,47%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>744131</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>741966</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1445301</t>
+          <t>1445662</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
